--- a/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/2mps_analysis.xlsx
+++ b/NURBS IDX30 PYTHON ANALYSIS/Back_final_15_2_26/30gps/2mps_analysis.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>Time</t>
   </si>
@@ -79,13 +79,34 @@
     <t>Q</t>
   </si>
   <si>
-    <t>rolling_std</t>
-  </si>
-  <si>
     <t>steady_state</t>
   </si>
   <si>
-    <t>avg_Q_steady</t>
+    <t>Averages</t>
+  </si>
+  <si>
+    <t>RTD_OUT_unc</t>
+  </si>
+  <si>
+    <t>RTD_IN_unc</t>
+  </si>
+  <si>
+    <t>RTD_unc</t>
+  </si>
+  <si>
+    <t>Delta_RTD</t>
+  </si>
+  <si>
+    <t>Rel_unc</t>
+  </si>
+  <si>
+    <t>ABS_unc</t>
+  </si>
+  <si>
+    <t>Average Q (W)</t>
+  </si>
+  <si>
+    <t>Average Q Uncertainty (W)</t>
   </si>
 </sst>
 </file>
@@ -421,10 +442,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:X12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:29">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -497,8 +518,23 @@
       <c r="X1" t="s">
         <v>23</v>
       </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:29">
       <c r="A2" s="1">
         <v>46068.65249233796</v>
       </c>
@@ -562,14 +598,32 @@
       <c r="U2">
         <v>447.4911574424236</v>
       </c>
-      <c r="W2" t="b">
-        <v>0</v>
+      <c r="V2" t="b">
+        <v>1</v>
+      </c>
+      <c r="W2" t="s">
+        <v>29</v>
       </c>
       <c r="X2">
-        <v>436.7410972261276</v>
+        <v>0.256452854</v>
+      </c>
+      <c r="Y2">
+        <v>0.263341582</v>
+      </c>
+      <c r="Z2">
+        <v>0.3675824467177507</v>
+      </c>
+      <c r="AA2">
+        <v>3.444364</v>
+      </c>
+      <c r="AB2">
+        <v>0.1071874688668815</v>
+      </c>
+      <c r="AC2">
+        <v>47.96544450656454</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:29">
       <c r="A3" s="1">
         <v>46068.6526080787</v>
       </c>
@@ -633,11 +687,32 @@
       <c r="U3">
         <v>438.172312866694</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
+      <c r="V3" t="b">
+        <v>1</v>
+      </c>
+      <c r="W3">
+        <v>438.7725734578966</v>
+      </c>
+      <c r="X3">
+        <v>0.256503746</v>
+      </c>
+      <c r="Y3">
+        <v>0.263368008</v>
+      </c>
+      <c r="Z3">
+        <v>0.3676368851868928</v>
+      </c>
+      <c r="AA3">
+        <v>3.432130999999998</v>
+      </c>
+      <c r="AB3">
+        <v>0.1075819859844065</v>
+      </c>
+      <c r="AC3">
+        <v>47.13944762157966</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:29">
       <c r="A4" s="1">
         <v>46068.65272439815</v>
       </c>
@@ -701,14 +776,32 @@
       <c r="U4">
         <v>439.6531787676564</v>
       </c>
-      <c r="V4">
-        <v>5.007789561429012</v>
-      </c>
-      <c r="W4" t="b">
-        <v>0</v>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="s">
+        <v>30</v>
+      </c>
+      <c r="X4">
+        <v>0.25655591</v>
+      </c>
+      <c r="Y4">
+        <v>0.263397618</v>
+      </c>
+      <c r="Z4">
+        <v>0.3676944929204162</v>
+      </c>
+      <c r="AA4">
+        <v>3.420853999999999</v>
+      </c>
+      <c r="AB4">
+        <v>0.1079503433825059</v>
+      </c>
+      <c r="AC4">
+        <v>47.46071161717874</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:29">
       <c r="A5" s="1">
         <v>46068.65284013889</v>
       </c>
@@ -772,14 +865,32 @@
       <c r="U5">
         <v>440.8705057448373</v>
       </c>
-      <c r="V5">
-        <v>1.351239776012361</v>
-      </c>
-      <c r="W5" t="b">
+      <c r="V5" t="b">
         <v>1</v>
       </c>
+      <c r="W5">
+        <v>47.47781991720957</v>
+      </c>
+      <c r="X5">
+        <v>0.256588036</v>
+      </c>
+      <c r="Y5">
+        <v>0.263424044</v>
+      </c>
+      <c r="Z5">
+        <v>0.3677358388512754</v>
+      </c>
+      <c r="AA5">
+        <v>3.418003999999996</v>
+      </c>
+      <c r="AB5">
+        <v>0.108051627034728</v>
+      </c>
+      <c r="AC5">
+        <v>47.63677545735305</v>
+      </c>
     </row>
-    <row r="6" spans="1:24">
+    <row r="6" spans="1:29">
       <c r="A6" s="1">
         <v>46068.65295645833</v>
       </c>
@@ -843,14 +954,29 @@
       <c r="U6">
         <v>435.6743510916135</v>
       </c>
-      <c r="V6">
-        <v>2.717626961929457</v>
-      </c>
-      <c r="W6" t="b">
+      <c r="V6" t="b">
         <v>1</v>
       </c>
+      <c r="X6">
+        <v>0.256622072</v>
+      </c>
+      <c r="Y6">
+        <v>0.26345429</v>
+      </c>
+      <c r="Z6">
+        <v>0.3677812539499223</v>
+      </c>
+      <c r="AA6">
+        <v>3.416108999999999</v>
+      </c>
+      <c r="AB6">
+        <v>0.1081242900991303</v>
+      </c>
+      <c r="AC6">
+        <v>47.10697992617995</v>
+      </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:29">
       <c r="A7" s="1">
         <v>46068.65307219907</v>
       </c>
@@ -914,14 +1040,29 @@
       <c r="U7">
         <v>440.9313159929989</v>
       </c>
-      <c r="V7">
-        <v>3.017708872663109</v>
-      </c>
-      <c r="W7" t="b">
-        <v>0</v>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>0.256647518</v>
+      </c>
+      <c r="Y7">
+        <v>0.2634683</v>
+      </c>
+      <c r="Z7">
+        <v>0.3678090450226181</v>
+      </c>
+      <c r="AA7">
+        <v>3.410390999999997</v>
+      </c>
+      <c r="AB7">
+        <v>0.108312140432012</v>
+      </c>
+      <c r="AC7">
+        <v>47.75821461870554</v>
       </c>
     </row>
-    <row r="8" spans="1:24">
+    <row r="8" spans="1:29">
       <c r="A8" s="1">
         <v>46068.65318793982</v>
       </c>
@@ -985,14 +1126,29 @@
       <c r="U8">
         <v>439.06891980489</v>
       </c>
-      <c r="V8">
-        <v>2.665436058291257</v>
-      </c>
-      <c r="W8" t="b">
+      <c r="V8" t="b">
         <v>1</v>
       </c>
+      <c r="X8">
+        <v>0.256662786</v>
+      </c>
+      <c r="Y8">
+        <v>0.263477534</v>
+      </c>
+      <c r="Z8">
+        <v>0.3678263131424979</v>
+      </c>
+      <c r="AA8">
+        <v>3.407374000000004</v>
+      </c>
+      <c r="AB8">
+        <v>0.1084122726686191</v>
+      </c>
+      <c r="AC8">
+        <v>47.60045945420378</v>
+      </c>
     </row>
-    <row r="9" spans="1:24">
+    <row r="9" spans="1:29">
       <c r="A9" s="1">
         <v>46068.65330368056</v>
       </c>
@@ -1056,14 +1212,29 @@
       <c r="U9">
         <v>435.0422256113749</v>
       </c>
-      <c r="V9">
-        <v>3.010098869154345</v>
-      </c>
-      <c r="W9" t="b">
-        <v>0</v>
+      <c r="V9" t="b">
+        <v>1</v>
+      </c>
+      <c r="X9">
+        <v>0.256679326</v>
+      </c>
+      <c r="Y9">
+        <v>0.263492498</v>
+      </c>
+      <c r="Z9">
+        <v>0.3678485733261639</v>
+      </c>
+      <c r="AA9">
+        <v>3.406585999999997</v>
+      </c>
+      <c r="AB9">
+        <v>0.1084436434990275</v>
+      </c>
+      <c r="AC9">
+        <v>47.17756402122344</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:29">
       <c r="A10" s="1">
         <v>46068.65342</v>
       </c>
@@ -1127,14 +1298,29 @@
       <c r="U10">
         <v>438.7263490984267</v>
       </c>
-      <c r="V10">
-        <v>2.232501835940268</v>
-      </c>
-      <c r="W10" t="b">
+      <c r="V10" t="b">
         <v>1</v>
       </c>
+      <c r="X10">
+        <v>0.256707954</v>
+      </c>
+      <c r="Y10">
+        <v>0.263507462</v>
+      </c>
+      <c r="Z10">
+        <v>0.3678792684788687</v>
+      </c>
+      <c r="AA10">
+        <v>3.399754000000001</v>
+      </c>
+      <c r="AB10">
+        <v>0.1086687062797378</v>
+      </c>
+      <c r="AC10">
+        <v>47.67582476735866</v>
+      </c>
     </row>
-    <row r="11" spans="1:24">
+    <row r="11" spans="1:29">
       <c r="A11" s="1">
         <v>46068.65353574074</v>
       </c>
@@ -1198,14 +1384,29 @@
       <c r="U11">
         <v>436.4821492101255</v>
       </c>
-      <c r="V11">
-        <v>1.856635800614274</v>
-      </c>
-      <c r="W11" t="b">
+      <c r="V11" t="b">
         <v>1</v>
       </c>
+      <c r="X11">
+        <v>0.256719088</v>
+      </c>
+      <c r="Y11">
+        <v>0.263512556</v>
+      </c>
+      <c r="Z11">
+        <v>0.3678906866355887</v>
+      </c>
+      <c r="AA11">
+        <v>3.396734000000002</v>
+      </c>
+      <c r="AB11">
+        <v>0.1087678519364833</v>
+      </c>
+      <c r="AC11">
+        <v>47.47522577820494</v>
+      </c>
     </row>
-    <row r="12" spans="1:24">
+    <row r="12" spans="1:29">
       <c r="A12" s="1">
         <v>46068.65365206019</v>
       </c>
@@ -1269,11 +1470,26 @@
       <c r="U12">
         <v>434.3858424058207</v>
       </c>
-      <c r="V12">
-        <v>2.170673232931136</v>
-      </c>
-      <c r="W12" t="b">
+      <c r="V12" t="b">
         <v>1</v>
+      </c>
+      <c r="X12">
+        <v>0.256726722</v>
+      </c>
+      <c r="Y12">
+        <v>0.263518606</v>
+      </c>
+      <c r="Z12">
+        <v>0.3679003472369231</v>
+      </c>
+      <c r="AA12">
+        <v>3.395942000000005</v>
+      </c>
+      <c r="AB12">
+        <v>0.1087958370351337</v>
+      </c>
+      <c r="AC12">
+        <v>47.25937132075294</v>
       </c>
     </row>
   </sheetData>
